--- a/logs/general_schedule_mk.xlsx
+++ b/logs/general_schedule_mk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monik\Documents\git\2025_g34p\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFD52F5-FAE7-4248-BE3D-2E73C0A16D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74533CD-C1C0-45AC-8996-02BE5A526CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="36">
   <si>
     <t>date</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>68 samples</t>
+  </si>
+  <si>
+    <t>seeds planted</t>
   </si>
 </sst>
 </file>
@@ -495,17 +498,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="77.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="77.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -522,7 +525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45847</v>
       </c>
@@ -540,7 +543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>45848</v>
       </c>
@@ -557,8 +560,11 @@
       <c r="E3" s="11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>45851</v>
       </c>
@@ -576,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45852</v>
       </c>
@@ -594,7 +600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45854</v>
       </c>
@@ -612,7 +618,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45856</v>
       </c>
@@ -630,7 +636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>45860</v>
       </c>
@@ -648,7 +654,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>45860</v>
       </c>
@@ -666,7 +672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45863</v>
       </c>
@@ -684,7 +690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45863</v>
       </c>
@@ -702,7 +708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>45870</v>
       </c>
@@ -720,7 +726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>45870</v>
       </c>
@@ -738,7 +744,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>45870</v>
       </c>
@@ -756,7 +762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>45870</v>
       </c>
@@ -774,7 +780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>45873</v>
       </c>
@@ -792,7 +798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>45873</v>
       </c>
@@ -810,7 +816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>45876</v>
       </c>
@@ -828,7 +834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>45876</v>
       </c>
@@ -846,7 +852,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>45880</v>
       </c>
@@ -864,7 +870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>45881</v>
       </c>
@@ -882,7 +888,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>45881</v>
       </c>
@@ -900,7 +906,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>45883</v>
       </c>
@@ -918,7 +924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>45884</v>
       </c>
@@ -936,7 +942,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>45887</v>
       </c>
@@ -954,7 +960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>45889</v>
       </c>
@@ -972,7 +978,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>45891</v>
       </c>
@@ -990,7 +996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>45894</v>
       </c>
@@ -1008,7 +1014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>45903</v>
       </c>
@@ -1026,7 +1032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>45905</v>
       </c>
@@ -1044,7 +1050,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>45906</v>
       </c>
@@ -1062,7 +1068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>45907</v>
       </c>
@@ -1080,7 +1086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>45907</v>
       </c>
@@ -1098,7 +1104,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>45909</v>
       </c>
@@ -1116,7 +1122,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>45913</v>
       </c>
@@ -1134,7 +1140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>45916</v>
       </c>
@@ -1149,7 +1155,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>45917</v>
       </c>
@@ -1167,7 +1173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>45919</v>
       </c>
@@ -1185,7 +1191,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>45920</v>
       </c>
@@ -1202,8 +1208,16 @@
       <c r="E39" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <f>A39-A3</f>
+        <v>72</v>
+      </c>
+      <c r="G39">
+        <f>F39/7</f>
+        <v>10.285714285714286</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>45927</v>
       </c>
@@ -1218,7 +1232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>45928</v>
       </c>
@@ -1233,7 +1247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>45931</v>
       </c>
@@ -1251,7 +1265,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>45961</v>
       </c>

--- a/logs/general_schedule_mk.xlsx
+++ b/logs/general_schedule_mk.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monik\Documents\git\2025_g34p\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74533CD-C1C0-45AC-8996-02BE5A526CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B296B7D-426B-4D7B-9A54-1F0BF166788C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
   <si>
     <t>date</t>
   </si>
@@ -147,6 +148,36 @@
   </si>
   <si>
     <t>seeds planted</t>
+  </si>
+  <si>
+    <t>I believe all the aboveground biomass was sampled</t>
+  </si>
+  <si>
+    <t>week of the year</t>
+  </si>
+  <si>
+    <t>week#</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>planted</t>
+  </si>
+  <si>
+    <t>p started</t>
+  </si>
+  <si>
+    <t>licor start</t>
+  </si>
+  <si>
+    <t>licor end</t>
+  </si>
+  <si>
+    <t>shoot biomass harvest</t>
+  </si>
+  <si>
+    <t>root biomass harvest</t>
   </si>
 </sst>
 </file>
@@ -173,7 +204,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -192,6 +223,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -205,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -218,6 +255,11 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="2" customWidth="1"/>
@@ -1283,6 +1325,14 @@
         <v>34</v>
       </c>
     </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>45953</v>
+      </c>
+      <c r="C44" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E42">
@@ -1291,4 +1341,277 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F452CAB-EDE0-4435-A33A-52B27FED579E}">
+  <dimension ref="C4:F21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:6" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C5" s="2">
+        <v>45848</v>
+      </c>
+      <c r="D5">
+        <f>WEEKNUM(C5)</f>
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="2">
+        <f>C5+7</f>
+        <v>45855</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D21" si="0">WEEKNUM(C6)</f>
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="2">
+        <f t="shared" ref="C7:C21" si="1">C6+7</f>
+        <v>45862</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="2">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="2">
+        <f t="shared" si="1"/>
+        <v>45876</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C10" s="13">
+        <f t="shared" si="1"/>
+        <v>45883</v>
+      </c>
+      <c r="D10" s="14">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="E10" s="14">
+        <v>6</v>
+      </c>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C11" s="13">
+        <f t="shared" si="1"/>
+        <v>45890</v>
+      </c>
+      <c r="D11" s="14">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="E11" s="14">
+        <v>7</v>
+      </c>
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C12" s="13">
+        <f t="shared" si="1"/>
+        <v>45897</v>
+      </c>
+      <c r="D12" s="14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="E12" s="14">
+        <v>8</v>
+      </c>
+      <c r="F12" s="14"/>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="2">
+        <f t="shared" si="1"/>
+        <v>45904</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C14" s="13">
+        <f t="shared" si="1"/>
+        <v>45911</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="E14" s="14">
+        <v>10</v>
+      </c>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="2">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="E15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C16" s="2">
+        <f t="shared" si="1"/>
+        <v>45925</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="E16">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="2">
+        <f>C16+7</f>
+        <v>45932</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="E17">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C18" s="2">
+        <f t="shared" si="1"/>
+        <v>45939</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="E18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C19" s="13">
+        <f t="shared" si="1"/>
+        <v>45946</v>
+      </c>
+      <c r="D19" s="14">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="E19" s="14">
+        <v>15</v>
+      </c>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C20" s="2">
+        <f t="shared" si="1"/>
+        <v>45953</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="E20">
+        <v>16</v>
+      </c>
+      <c r="F20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C21" s="2">
+        <f t="shared" si="1"/>
+        <v>45960</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="E21">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/logs/general_schedule_mk.xlsx
+++ b/logs/general_schedule_mk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monik\Documents\git\2025_g34p\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B296B7D-426B-4D7B-9A54-1F0BF166788C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C486233-358B-4A1E-B8DF-A3429C1E6418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="49">
   <si>
     <t>date</t>
   </si>
@@ -178,6 +178,15 @@
   </si>
   <si>
     <t>root biomass harvest</t>
+  </si>
+  <si>
+    <t>PHE</t>
+  </si>
+  <si>
+    <t>Full PHE</t>
+  </si>
+  <si>
+    <t>Partial</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F452CAB-EDE0-4435-A33A-52B27FED579E}">
-  <dimension ref="C4:F21"/>
+  <dimension ref="C4:G21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.5546875" customWidth="1"/>
@@ -1354,7 +1363,7 @@
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:6" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1377,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C5" s="2">
         <v>45848</v>
       </c>
@@ -1383,7 +1392,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C6" s="2">
         <f>C5+7</f>
         <v>45855</v>
@@ -1396,7 +1405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C7" s="2">
         <f t="shared" ref="C7:C21" si="1">C6+7</f>
         <v>45862</v>
@@ -1409,7 +1418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C8" s="2">
         <f t="shared" si="1"/>
         <v>45869</v>
@@ -1422,7 +1431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C9" s="2">
         <f t="shared" si="1"/>
         <v>45876</v>
@@ -1438,7 +1447,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C10" s="13">
         <f t="shared" si="1"/>
         <v>45883</v>
@@ -1451,8 +1460,11 @@
         <v>6</v>
       </c>
       <c r="F10" s="14"/>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C11" s="13">
         <f t="shared" si="1"/>
         <v>45890</v>
@@ -1464,9 +1476,14 @@
       <c r="E11" s="14">
         <v>7</v>
       </c>
-      <c r="F11" s="14"/>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C12" s="13">
         <f t="shared" si="1"/>
         <v>45897</v>
@@ -1478,9 +1495,14 @@
       <c r="E12" s="14">
         <v>8</v>
       </c>
-      <c r="F12" s="14"/>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="F12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C13" s="2">
         <f t="shared" si="1"/>
         <v>45904</v>
@@ -1492,8 +1514,11 @@
       <c r="E13">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C14" s="13">
         <f t="shared" si="1"/>
         <v>45911</v>
@@ -1505,9 +1530,14 @@
       <c r="E14" s="14">
         <v>10</v>
       </c>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="F14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C15" s="2">
         <f t="shared" si="1"/>
         <v>45918</v>
@@ -1520,7 +1550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C16" s="2">
         <f t="shared" si="1"/>
         <v>45925</v>

--- a/logs/general_schedule_mk.xlsx
+++ b/logs/general_schedule_mk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monik\Documents\git\2025_g34p\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C486233-358B-4A1E-B8DF-A3429C1E6418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0780A10-BD54-48CE-9B3D-F3FB10F3757F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1354,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F452CAB-EDE0-4435-A33A-52B27FED579E}">
-  <dimension ref="C4:G21"/>
+  <dimension ref="C3:J21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.5546875" customWidth="1"/>
@@ -1363,7 +1363,12 @@
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
@@ -1376,8 +1381,11 @@
       <c r="F4" s="12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J4" s="12">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C5" s="2">
         <v>45848</v>
       </c>
@@ -1391,8 +1399,12 @@
       <c r="F5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <f>J3-J4</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C6" s="2">
         <f>C5+7</f>
         <v>45855</v>
@@ -1405,7 +1417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C7" s="2">
         <f t="shared" ref="C7:C21" si="1">C6+7</f>
         <v>45862</v>
@@ -1418,7 +1430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C8" s="2">
         <f t="shared" si="1"/>
         <v>45869</v>
@@ -1431,7 +1443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C9" s="2">
         <f t="shared" si="1"/>
         <v>45876</v>
@@ -1447,7 +1459,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C10" s="13">
         <f t="shared" si="1"/>
         <v>45883</v>
@@ -1464,7 +1476,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C11" s="13">
         <f t="shared" si="1"/>
         <v>45890</v>
@@ -1483,7 +1495,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C12" s="13">
         <f t="shared" si="1"/>
         <v>45897</v>
@@ -1502,7 +1514,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C13" s="2">
         <f t="shared" si="1"/>
         <v>45904</v>
@@ -1518,7 +1530,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C14" s="13">
         <f t="shared" si="1"/>
         <v>45911</v>
@@ -1537,7 +1549,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C15" s="2">
         <f t="shared" si="1"/>
         <v>45918</v>
@@ -1550,7 +1562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C16" s="2">
         <f t="shared" si="1"/>
         <v>45925</v>

--- a/logs/general_schedule_mk.xlsx
+++ b/logs/general_schedule_mk.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monik\Documents\git\2025_g34p\logs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Work\Documents\Git\2025_g34p\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0780A10-BD54-48CE-9B3D-F3FB10F3757F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABAFD96-B0B5-4548-812D-2589A82E4C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-165" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="47">
   <si>
     <t>date</t>
   </si>
@@ -156,37 +156,31 @@
     <t>week of the year</t>
   </si>
   <si>
-    <t>week#</t>
-  </si>
-  <si>
     <t>event</t>
   </si>
   <si>
-    <t>planted</t>
-  </si>
-  <si>
-    <t>p started</t>
-  </si>
-  <si>
-    <t>licor start</t>
-  </si>
-  <si>
-    <t>licor end</t>
-  </si>
-  <si>
-    <t>shoot biomass harvest</t>
-  </si>
-  <si>
-    <t>root biomass harvest</t>
-  </si>
-  <si>
-    <t>PHE</t>
-  </si>
-  <si>
-    <t>Full PHE</t>
-  </si>
-  <si>
-    <t>Partial</t>
+    <t>phenology</t>
+  </si>
+  <si>
+    <t>phenology, harvest shoots</t>
+  </si>
+  <si>
+    <t>harvest roots</t>
+  </si>
+  <si>
+    <t>li600</t>
+  </si>
+  <si>
+    <t>li6800</t>
+  </si>
+  <si>
+    <t>treatments started</t>
+  </si>
+  <si>
+    <t>Total weeks</t>
+  </si>
+  <si>
+    <t>phenology, last phosphorous fertilization 9/17</t>
   </si>
 </sst>
 </file>
@@ -213,7 +207,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,12 +228,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -247,11 +247,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -267,8 +282,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,16 +587,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
-    <col min="5" max="5" width="77.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="77.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -576,7 +613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45847</v>
       </c>
@@ -594,7 +631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>45848</v>
       </c>
@@ -615,7 +652,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45851</v>
       </c>
@@ -633,7 +670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45852</v>
       </c>
@@ -651,7 +688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45854</v>
       </c>
@@ -669,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45856</v>
       </c>
@@ -687,7 +724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>45860</v>
       </c>
@@ -705,7 +742,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45860</v>
       </c>
@@ -723,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45863</v>
       </c>
@@ -741,7 +778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45863</v>
       </c>
@@ -759,7 +796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45870</v>
       </c>
@@ -777,7 +814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45870</v>
       </c>
@@ -795,7 +832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45870</v>
       </c>
@@ -813,7 +850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45870</v>
       </c>
@@ -831,7 +868,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45873</v>
       </c>
@@ -849,7 +886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45873</v>
       </c>
@@ -867,7 +904,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45876</v>
       </c>
@@ -885,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45876</v>
       </c>
@@ -903,7 +940,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>45880</v>
       </c>
@@ -921,7 +958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>45881</v>
       </c>
@@ -939,7 +976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>45881</v>
       </c>
@@ -957,7 +994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>45883</v>
       </c>
@@ -975,7 +1012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>45884</v>
       </c>
@@ -993,7 +1030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45887</v>
       </c>
@@ -1011,7 +1048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>45889</v>
       </c>
@@ -1029,7 +1066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>45891</v>
       </c>
@@ -1047,7 +1084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>45894</v>
       </c>
@@ -1065,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>45903</v>
       </c>
@@ -1083,7 +1120,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>45905</v>
       </c>
@@ -1101,7 +1138,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>45906</v>
       </c>
@@ -1119,7 +1156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>45907</v>
       </c>
@@ -1137,7 +1174,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>45907</v>
       </c>
@@ -1155,7 +1192,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>45909</v>
       </c>
@@ -1173,7 +1210,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>45913</v>
       </c>
@@ -1191,7 +1228,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>45916</v>
       </c>
@@ -1206,7 +1243,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>45917</v>
       </c>
@@ -1224,7 +1261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>45919</v>
       </c>
@@ -1242,7 +1279,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>45920</v>
       </c>
@@ -1268,7 +1305,7 @@
         <v>10.285714285714286</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>45927</v>
       </c>
@@ -1283,7 +1320,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>45928</v>
       </c>
@@ -1298,7 +1335,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>45931</v>
       </c>
@@ -1316,7 +1353,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>45961</v>
       </c>
@@ -1334,7 +1371,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>45953</v>
       </c>
@@ -1354,306 +1391,248 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F452CAB-EDE0-4435-A33A-52B27FED579E}">
-  <dimension ref="C3:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="C4:E23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" customWidth="1"/>
-    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="J3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="3:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="12" t="s">
+    <row r="4" spans="3:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="12">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="2">
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="13">
         <v>45848</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="20">
         <f>WEEKNUM(C5)</f>
         <v>28</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5">
-        <f>J3-J4</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="2">
+      <c r="E5" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="13">
         <f>C5+7</f>
         <v>45855</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="20">
         <f t="shared" ref="D6:D21" si="0">WEEKNUM(C6)</f>
         <v>29</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="2">
+      <c r="E6" s="14"/>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="13">
         <f t="shared" ref="C7:C21" si="1">C6+7</f>
         <v>45862</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="20">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="2">
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="13">
         <f t="shared" si="1"/>
         <v>45869</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="20">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="E8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="2">
+      <c r="E8" s="14"/>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="22">
         <f t="shared" si="1"/>
         <v>45876</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="23">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="13">
+      <c r="E9" s="24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="15">
         <f t="shared" si="1"/>
         <v>45883</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="21">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="E10" s="14">
-        <v>6</v>
-      </c>
-      <c r="F10" s="14"/>
-      <c r="G10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="13">
+      <c r="E10" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="15">
         <f t="shared" si="1"/>
         <v>45890</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="21">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="E11" s="14">
-        <v>7</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="13">
+      <c r="E11" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="15">
         <f t="shared" si="1"/>
         <v>45897</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="21">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="E12" s="14">
-        <v>8</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="2">
+      <c r="E12" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="15">
         <f t="shared" si="1"/>
         <v>45904</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="21">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="E13">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="13">
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="15">
         <f t="shared" si="1"/>
         <v>45911</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="21">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="E14" s="14">
-        <v>10</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="2">
+      <c r="E14" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="15">
         <f t="shared" si="1"/>
         <v>45918</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="21">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="E15">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="2">
+      <c r="E15" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="22">
         <f t="shared" si="1"/>
         <v>45925</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="23">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="E16">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" s="2">
+      <c r="E16" s="24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="22">
         <f>C16+7</f>
         <v>45932</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="23">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="E17">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E17" s="24" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C18" s="2">
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="22">
         <f t="shared" si="1"/>
         <v>45939</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="23">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="E18">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C19" s="13">
+      <c r="E18" s="24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="22">
         <f t="shared" si="1"/>
         <v>45946</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="23">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="E19" s="14">
-        <v>15</v>
-      </c>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C20" s="2">
+      <c r="E19" s="24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="15">
         <f t="shared" si="1"/>
         <v>45953</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="21">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="E20">
-        <v>16</v>
-      </c>
-      <c r="F20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C21" s="2">
+      <c r="E20" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="15">
         <f t="shared" si="1"/>
         <v>45960</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="21">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="20">
         <v>17</v>
       </c>
-      <c r="F21" t="s">
-        <v>45</v>
-      </c>
+      <c r="E23" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>